--- a/data/trans_dic/IP07_C12_R_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C12_R_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan, percibido por el menor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 23,73</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 31,59</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2,13; 20,99</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,47; 4,34</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,78; 5,45</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,89; 3,67</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 12,73</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,59</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,06; 8,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,07; 4,91</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,2; 5,25</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 4,15</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.05350857632145614</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1037174597163542</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.07631417877754763</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.02131272303100862</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3978</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4407</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>655; 6447</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.2372963048415732</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3159325715940066</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2098967975305515</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.01604715167012421</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.02286433916126002</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.01888270347918827</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3215</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3262</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6477</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.00472020529951713</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.007802224377504411</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.008866741061823726</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>946; 8702</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1113; 7776</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3041; 12603</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04343907235334911</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.05450088021519484</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.03674356024406853</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.04623766730367301</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.01445475671762051</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.03238144841770794</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2451</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3043</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.01124954765312675</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.01056772854634649</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>596; 6745</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2701</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>993; 7687</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.1272576255524518</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.0659246795614275</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.08180285169936435</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.02429662544750651</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.02682909413134609</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.0253665382348124</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>6563</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5301</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11864</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.01068589284417778</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01204823424931005</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.01409992516507498</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2886; 13268</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>2381; 10372</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>6594; 19388</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.04912178665749573</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.05249164220106079</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.04145401702849508</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen mucho o muchísimo cansancio para disfrutar de las cosas que le gustan, percibido por el menor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>897</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1447</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3978</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>4407</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>6447</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3215</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>3262</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>6477</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>946</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>8702</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>7776</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12603</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2451</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>592</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>596</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>6745</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2701</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>7687</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>6563</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>5301</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>11864</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>2381</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>6594</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>13268</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>10372</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>19388</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>